--- a/Data/lab_screening/participant_excluded_review.xlsx
+++ b/Data/lab_screening/participant_excluded_review.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Tulum/Dropbox/Github/Creativity-in-ADHD/Data/lab_screening/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E2C809-F47F-A740-9479-3F44002E5FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38388D68-35EB-B74A-ABE1-37348033622A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2600" yWindow="1620" windowWidth="29420" windowHeight="14480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1620" windowWidth="28800" windowHeight="14480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$22</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
@@ -188,15 +191,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -634,10 +635,10 @@
       <c r="C8" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" t="s">
         <v>34</v>
       </c>
     </row>
@@ -685,10 +686,10 @@
       <c r="C11" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" t="s">
         <v>34</v>
       </c>
     </row>
@@ -880,6 +881,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I22" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data/lab_screening/participant_excluded_review.xlsx
+++ b/Data/lab_screening/participant_excluded_review.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Tulum/Dropbox/Github/Creativity-in-ADHD/Data/lab_screening/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38388D68-35EB-B74A-ABE1-37348033622A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{149235C9-5B3C-4344-BAA9-2CABF03AC9BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1620" windowWidth="28800" windowHeight="14480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$26</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="45">
   <si>
     <t>subjectid</t>
   </si>
@@ -143,6 +143,21 @@
   </si>
   <si>
     <t>exlusion_reason</t>
+  </si>
+  <si>
+    <t>missing group assignment</t>
+  </si>
+  <si>
+    <t>YyLeol</t>
+  </si>
+  <si>
+    <t>fzgsNA</t>
+  </si>
+  <si>
+    <t>95xyap</t>
+  </si>
+  <si>
+    <t>kPjb3e</t>
   </si>
 </sst>
 </file>
@@ -502,12 +517,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="4" width="17.6640625" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" customWidth="1"/>
+    <col min="5" max="5" width="29.5" customWidth="1"/>
     <col min="9" max="9" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -880,8 +896,40 @@
         <v>7</v>
       </c>
     </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I22" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I26" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>